--- a/etf_holdings/2026-10-02_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00405A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:36</t>
+          <t>2026-10-02 19:06:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,33 +509,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+3.4%1215</t>
+          <t>+7.41%1305</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>+7.41%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1215</v>
+        <v>1305</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.98%1,920,000</t>
+          <t>10.18%2,020,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.98%</t>
+          <t>10.18%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1920000</v>
+        <v>2020000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:36</t>
+          <t>2026-10-02 19:06:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.1%6875</t>
+          <t>-1.09%6800</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6875</v>
+        <v>6800</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.88%260,000</t>
+          <t>6.83%260,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.88%</t>
+          <t>6.83%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:36</t>
+          <t>2026-10-02 19:06:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.22%4980</t>
+          <t>-1.85%5030</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4980</v>
+        <v>5030</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.60%344,000</t>
+          <t>6.62%323,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.60%</t>
+          <t>6.62%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>344000</v>
+        <v>323000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:36</t>
+          <t>2026-10-02 19:06:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-1.54%2555</t>
+          <t>-0.6%4950</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2555</v>
+        <v>4950</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.54%665,000</t>
+          <t>6.58%344,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.54%</t>
+          <t>6.58%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>665000</v>
+        <v>344000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:36</t>
+          <t>2026-10-02 19:06:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.74%7900</t>
+          <t>-0.59%2540</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>7900</v>
+        <v>2540</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.48%213,000</t>
+          <t>6.52%665,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.48%</t>
+          <t>6.52%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>213000</v>
+        <v>665000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:36</t>
+          <t>2026-10-02 19:06:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.85%5030</t>
+          <t>0%7900</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5030</v>
+        <v>7900</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.26%323,000</t>
+          <t>6.50%213,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.26%</t>
+          <t>6.50%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>323000</v>
+        <v>213000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:36</t>
+          <t>2026-10-02 19:06:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.23%1095</t>
+          <t>+2.82%1460</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1095</v>
+        <v>1460</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.75%1,127,000</t>
+          <t>5.97%1,059,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>5.97%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1127000</v>
+        <v>1059000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:36</t>
+          <t>2026-10-02 19:06:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+5.97%1420</t>
+          <t>+0.91%1105</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+5.97%</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1420</v>
+        <v>1105</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.70%859,000</t>
+          <t>4.81%1,127,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.70%</t>
+          <t>4.81%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>859000</v>
+        <v>1127000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:36</t>
+          <t>2026-10-02 19:06:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.81%4975</t>
+          <t>+4.22%5185</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>+4.22%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4975</v>
+        <v>5185</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.06%212,000</t>
+          <t>4.25%212,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>4.25%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:36</t>
+          <t>2026-10-02 19:06:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.65%2390</t>
+          <t>+3.42%1965</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.65%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2390</v>
+        <v>1965</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.06%441,000</t>
+          <t>4.01%529,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>441000</v>
+        <v>529000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:36</t>
+          <t>2026-10-02 19:06:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,25 +1114,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.55%19040</t>
+          <t>+7.18%1000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>+7.18%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>19040</v>
+        <v>1000</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.98%54,300</t>
+          <t>3.98%1,030,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1141,11 +1141,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>54300</v>
+        <v>1030000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:36</t>
+          <t>2026-10-02 19:06:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+7.04%1900</t>
+          <t>+1.55%19040</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+7.04%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1900</v>
+        <v>19040</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.87%529,000</t>
+          <t>3.95%54,300</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>3.95%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>529000</v>
+        <v>54300</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:36</t>
+          <t>2026-10-02 19:06:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+2.18%3510</t>
+          <t>-3.35%2310</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-3.35%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3510</v>
+        <v>2310</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.76%278,000</t>
+          <t>3.93%441,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>3.93%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>278000</v>
+        <v>441000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:36</t>
+          <t>2026-10-02 19:06:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.65%933</t>
+          <t>-1.99%3440</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>933</v>
+        <v>3440</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.70%1,030,000</t>
+          <t>3.69%278,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.69%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1030000</v>
+        <v>278000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:36</t>
+          <t>2026-10-02 19:06:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.27%5490</t>
+          <t>+1.64%5580</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5490</v>
+        <v>5580</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.54%120,000</t>
+          <t>2.59%120,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.59%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:37</t>
+          <t>2026-10-02 19:06:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.82%11835</t>
+          <t>+2.62%12145</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>11835</v>
+        <v>12145</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.91%42,000</t>
+          <t>1.97%42,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:37</t>
+          <t>2026-10-02 19:06:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.81%306,000</t>
+          <t>1.91%306,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:37</t>
+          <t>2026-10-02 19:06:12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.12%3000</t>
+          <t>-0.4%2500</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.79%155,000</t>
+          <t>1.73%179,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>155000</v>
+        <v>179000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:37</t>
+          <t>2026-10-02 19:06:12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1.21%2510</t>
+          <t>-3.51%1510</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2510</v>
+        <v>1510</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.73%179,000</t>
+          <t>1.64%282,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.64%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>179000</v>
+        <v>282000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:37</t>
+          <t>2026-10-02 19:06:12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.49%1565</t>
+          <t>-2.12%3000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1565</v>
+        <v>3000</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.70%282,000</t>
+          <t>1.19%100,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>282000</v>
+        <v>100000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:37</t>
+          <t>2026-10-02 19:06:12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6278台表科</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.69%216.5</t>
+          <t>0%161.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>216.5</v>
+        <v>161.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.17%1,400,000</t>
+          <t>1.11%1,778,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1400000</v>
+        <v>1778000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:37</t>
+          <t>2026-10-02 19:06:12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+4.53%161.5</t>
+          <t>-1.18%2085</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>161.5</v>
+        <v>2085</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.11%1,778,000</t>
+          <t>0.80%99,139</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1778000</v>
+        <v>99139</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:37</t>
+          <t>2026-10-02 19:06:12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.96%2110</t>
+          <t>-2.67%1275</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-2.67%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2110</v>
+        <v>1275</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.81%99,139</t>
+          <t>0.77%148,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>99139</v>
+        <v>148000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:37</t>
+          <t>2026-10-02 19:06:12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-2.67%1275</t>
+          <t>+2.36%260</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-2.67%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1275</v>
+        <v>260</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.73%148,000</t>
+          <t>0.70%700,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>148000</v>
+        <v>700000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:37</t>
+          <t>2026-10-02 19:06:12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+0.79%1905</t>
+          <t>-1.05%1885</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1905</v>
+        <v>1885</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.69%94,000</t>
+          <t>0.68%94,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:37</t>
+          <t>2026-10-02 19:06:12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.59%254</t>
+          <t>+5.2%6070</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>+5.2%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>254</v>
+        <v>6070</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.68%700,000</t>
+          <t>0.54%23,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>700000</v>
+        <v>23000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:37</t>
+          <t>2026-10-02 19:06:12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>3450聯鈞</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.7%5770</t>
+          <t>+5.44%543</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>+5.44%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5770</v>
+        <v>543</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.51%23,000</t>
+          <t>0.52%250,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>23000</v>
+        <v>250000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:37</t>
+          <t>2026-10-02 19:06:12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3450聯鈞</t>
+          <t>6526達發</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.53%515</t>
+          <t>+0.72%835</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>+0.72%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>515</v>
+        <v>835</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.50%250,000</t>
+          <t>0.47%146,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>250000</v>
+        <v>146000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:37</t>
+          <t>2026-10-02 19:06:12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6526達發</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.31%829</t>
+          <t>+3.96%1050</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>+3.96%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>829</v>
+        <v>1050</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.47%146,000</t>
+          <t>0.20%50,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>146000</v>
+        <v>50000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:37</t>
+          <t>2026-10-02 19:06:12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.21%235.5</t>
+          <t>+1.93%184.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>235.5</v>
+        <v>184.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.36%400,000</t>
+          <t>0.15%211,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>400000</v>
+        <v>211000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:38</t>
+          <t>2026-10-02 19:06:13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7734印能科技</t>
+          <t>6285啟碁</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+4.88%2795</t>
+          <t>+1.06%238</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+4.88%</t>
+          <t>+1.06%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2795</v>
+        <v>238</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.32%30,000</t>
+          <t>0.09%100,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.09%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:38</t>
+          <t>2026-10-02 19:06:13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,34 +2395,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4749新應材</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.17%757</t>
+          <t>-0.17%295.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>757</v>
+        <v>295.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.28%95,000</t>
+          <t>0.05%42,650</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>95000</v>
+        <v>42650</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:38</t>
+          <t>2026-10-02 19:06:13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+4.12%1010</t>
+          <t>+0.82%245.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+4.12%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1010</v>
+        <v>245.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.19%50,000</t>
+          <t>0.03%34,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>50000</v>
+        <v>34000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:38</t>
+          <t>2026-10-02 19:06:13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,34 +2517,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.93%184.5</t>
+          <t>+9.94%553</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>184.5</v>
+        <v>553</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.15%211,000</t>
+          <t>0.02%10,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>211000</v>
+        <v>10000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:38</t>
+          <t>2026-10-02 19:06:13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,34 +2578,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4576大銀微系統</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.64%237.5</t>
+          <t>+1.2%3810</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>237.5</v>
+        <v>3810</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.07%72,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>72000</v>
+        <v>1000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:38</t>
+          <t>2026-10-02 19:06:13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.51%296</t>
+          <t>-0.97%716</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>296</v>
+        <v>716</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.05%42,650</t>
+          <t>0.01%5,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>42650</v>
+        <v>5000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:38</t>
+          <t>2026-10-02 19:06:13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,34 +2700,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.82%245.5</t>
+          <t>+0.23%217</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>245.5</v>
+        <v>217</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.03%34,000</t>
+          <t>&lt;0.01%10,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>34000</v>
+        <v>10000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:38</t>
+          <t>2026-10-02 19:06:13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+3.5%503</t>
+          <t>+0.42%713</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+3.5%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>503</v>
+        <v>713</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.02%10,000</t>
+          <t>&lt;0.01%3,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:38</t>
+          <t>2026-10-02 19:06:13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,30 +2822,30 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>3533嘉澤</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.67%3765</t>
+          <t>0%1855</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3765</v>
+        <v>1855</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.01%1,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:38</t>
+          <t>2026-10-02 19:06:13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,34 +2883,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>3605宏致</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.41%723</t>
+          <t>-4.21%170.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-4.21%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>723</v>
+        <v>170.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.01%5,000</t>
+          <t>&lt;0.01%10,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:38</t>
+          <t>2026-10-02 19:06:13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,25 +2944,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1%710</t>
+          <t>-0.67%1490</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>710</v>
+        <v>1490</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>&lt;0.01%3,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2971,11 +2971,11 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:38</t>
+          <t>2026-10-02 19:06:13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,21 +3005,21 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3533嘉澤</t>
+          <t>1590亞德客-KY</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+4.8%1855</t>
+          <t>-0.42%1180</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+4.8%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1855</v>
+        <v>1180</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:38</t>
+          <t>2026-10-02 19:06:13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3605宏致</t>
+          <t>4576大銀微系統</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+4.4%178</t>
+          <t>-1.47%234</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+4.4%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>178</v>
+        <v>234</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>&lt;0.01%10,000</t>
+          <t>&lt;0.01%2,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:38</t>
+          <t>2026-10-02 19:06:13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,21 +3127,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>8028昇陽半導體</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.67%1490</t>
+          <t>+1.25%283.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1490</v>
+        <v>283.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,71 +3158,10 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:27:38</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>1590亞德客-KY</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>-1.25%1185</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>-1.25%</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>1185</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>&lt;0.01%1,000</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-10-02_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:10</t>
+          <t>2026-10-02 22:50:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:10</t>
+          <t>2026-10-02 22:50:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:10</t>
+          <t>2026-10-02 22:50:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:10</t>
+          <t>2026-10-02 22:50:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:10</t>
+          <t>2026-10-02 22:50:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:10</t>
+          <t>2026-10-02 22:50:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:10</t>
+          <t>2026-10-02 22:50:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:10</t>
+          <t>2026-10-02 22:50:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:10</t>
+          <t>2026-10-02 22:50:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:10</t>
+          <t>2026-10-02 22:50:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:10</t>
+          <t>2026-10-02 22:50:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:10</t>
+          <t>2026-10-02 22:50:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:10</t>
+          <t>2026-10-02 22:50:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:10</t>
+          <t>2026-10-02 22:50:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:10</t>
+          <t>2026-10-02 22:50:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:12</t>
+          <t>2026-10-02 22:50:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:12</t>
+          <t>2026-10-02 22:50:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:12</t>
+          <t>2026-10-02 22:50:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:12</t>
+          <t>2026-10-02 22:50:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:12</t>
+          <t>2026-10-02 22:50:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:12</t>
+          <t>2026-10-02 22:50:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:12</t>
+          <t>2026-10-02 22:50:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:12</t>
+          <t>2026-10-02 22:50:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:12</t>
+          <t>2026-10-02 22:50:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:12</t>
+          <t>2026-10-02 22:50:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:12</t>
+          <t>2026-10-02 22:50:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:12</t>
+          <t>2026-10-02 22:50:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:12</t>
+          <t>2026-10-02 22:50:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:12</t>
+          <t>2026-10-02 22:50:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:12</t>
+          <t>2026-10-02 22:50:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:13</t>
+          <t>2026-10-02 22:50:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:13</t>
+          <t>2026-10-02 22:50:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:13</t>
+          <t>2026-10-02 22:50:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:13</t>
+          <t>2026-10-02 22:50:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:13</t>
+          <t>2026-10-02 22:50:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:13</t>
+          <t>2026-10-02 22:50:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:13</t>
+          <t>2026-10-02 22:50:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:13</t>
+          <t>2026-10-02 22:50:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:13</t>
+          <t>2026-10-02 22:50:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:13</t>
+          <t>2026-10-02 22:50:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:13</t>
+          <t>2026-10-02 22:50:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:13</t>
+          <t>2026-10-02 22:50:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:13</t>
+          <t>2026-10-02 22:50:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:13</t>
+          <t>2026-10-02 22:50:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">

--- a/etf_holdings/2026-10-02_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:39</t>
+          <t>2026-10-02 22:59:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:39</t>
+          <t>2026-10-02 22:59:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:39</t>
+          <t>2026-10-02 22:59:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:39</t>
+          <t>2026-10-02 22:59:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:39</t>
+          <t>2026-10-02 22:59:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:39</t>
+          <t>2026-10-02 22:59:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:39</t>
+          <t>2026-10-02 22:59:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:39</t>
+          <t>2026-10-02 22:59:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:39</t>
+          <t>2026-10-02 22:59:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:39</t>
+          <t>2026-10-02 22:59:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:39</t>
+          <t>2026-10-02 22:59:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:39</t>
+          <t>2026-10-02 22:59:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:39</t>
+          <t>2026-10-02 22:59:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:39</t>
+          <t>2026-10-02 22:59:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:39</t>
+          <t>2026-10-02 22:59:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:41</t>
+          <t>2026-10-02 22:59:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:41</t>
+          <t>2026-10-02 22:59:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:41</t>
+          <t>2026-10-02 22:59:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:41</t>
+          <t>2026-10-02 22:59:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:41</t>
+          <t>2026-10-02 22:59:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:41</t>
+          <t>2026-10-02 22:59:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:41</t>
+          <t>2026-10-02 22:59:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:41</t>
+          <t>2026-10-02 22:59:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:41</t>
+          <t>2026-10-02 22:59:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:41</t>
+          <t>2026-10-02 22:59:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:41</t>
+          <t>2026-10-02 22:59:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:41</t>
+          <t>2026-10-02 22:59:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:41</t>
+          <t>2026-10-02 22:59:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:41</t>
+          <t>2026-10-02 22:59:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:41</t>
+          <t>2026-10-02 22:59:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:42</t>
+          <t>2026-10-02 22:59:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:42</t>
+          <t>2026-10-02 22:59:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:42</t>
+          <t>2026-10-02 22:59:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:42</t>
+          <t>2026-10-02 22:59:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:42</t>
+          <t>2026-10-02 22:59:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:42</t>
+          <t>2026-10-02 22:59:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:42</t>
+          <t>2026-10-02 22:59:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:42</t>
+          <t>2026-10-02 22:59:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:42</t>
+          <t>2026-10-02 22:59:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:42</t>
+          <t>2026-10-02 22:59:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:42</t>
+          <t>2026-10-02 22:59:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:42</t>
+          <t>2026-10-02 22:59:22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:42</t>
+          <t>2026-10-02 22:59:22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:42</t>
+          <t>2026-10-02 22:59:22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">

--- a/etf_holdings/2026-10-02_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:19</t>
+          <t>2026-10-02 23:49:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:19</t>
+          <t>2026-10-02 23:49:01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:19</t>
+          <t>2026-10-02 23:49:01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:19</t>
+          <t>2026-10-02 23:49:01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:19</t>
+          <t>2026-10-02 23:49:01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:19</t>
+          <t>2026-10-02 23:49:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:19</t>
+          <t>2026-10-02 23:49:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:19</t>
+          <t>2026-10-02 23:49:01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:19</t>
+          <t>2026-10-02 23:49:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:19</t>
+          <t>2026-10-02 23:49:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:19</t>
+          <t>2026-10-02 23:49:01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:19</t>
+          <t>2026-10-02 23:49:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:19</t>
+          <t>2026-10-02 23:49:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:19</t>
+          <t>2026-10-02 23:49:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:19</t>
+          <t>2026-10-02 23:49:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:20</t>
+          <t>2026-10-02 23:49:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:20</t>
+          <t>2026-10-02 23:49:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:20</t>
+          <t>2026-10-02 23:49:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:20</t>
+          <t>2026-10-02 23:49:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:20</t>
+          <t>2026-10-02 23:49:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:20</t>
+          <t>2026-10-02 23:49:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:20</t>
+          <t>2026-10-02 23:49:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:20</t>
+          <t>2026-10-02 23:49:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:20</t>
+          <t>2026-10-02 23:49:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:20</t>
+          <t>2026-10-02 23:49:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:20</t>
+          <t>2026-10-02 23:49:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:20</t>
+          <t>2026-10-02 23:49:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:20</t>
+          <t>2026-10-02 23:49:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:20</t>
+          <t>2026-10-02 23:49:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:20</t>
+          <t>2026-10-02 23:49:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:22</t>
+          <t>2026-10-02 23:49:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:22</t>
+          <t>2026-10-02 23:49:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:22</t>
+          <t>2026-10-02 23:49:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:22</t>
+          <t>2026-10-02 23:49:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:22</t>
+          <t>2026-10-02 23:49:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:22</t>
+          <t>2026-10-02 23:49:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:22</t>
+          <t>2026-10-02 23:49:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:22</t>
+          <t>2026-10-02 23:49:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:22</t>
+          <t>2026-10-02 23:49:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:22</t>
+          <t>2026-10-02 23:49:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:22</t>
+          <t>2026-10-02 23:49:03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:22</t>
+          <t>2026-10-02 23:49:03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:22</t>
+          <t>2026-10-02 23:49:03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:22</t>
+          <t>2026-10-02 23:49:03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
